--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED04.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED04.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:52+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>161W</t>
+          <t>206W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L5"/>
+  <dimension ref="B2:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1697,116 +1697,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-3-0168</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>76W</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>第3年</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>3季</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>第3年4季</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-4-0138</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>61W</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>第4年</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>4季</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>第4年4季</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:L2"/>
@@ -1821,7 +1711,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G55"/>
+  <dimension ref="B2:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2141,10 +2031,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="E14" t="n">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2043,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2060,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,14 +2079,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Auction_Win</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-10</v>
+        <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2205,7 +2095,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>auction_bid_fee | {"order_id": "SIM_XA_FIXED-2-0165"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2222,11 +2112,11 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>第2年2季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2248,11 +2138,11 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2267,14 +2157,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E19" t="n">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2283,7 +2173,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-01dc25c17a"}</t>
         </is>
       </c>
     </row>
@@ -2293,14 +2183,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2309,7 +2199,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-01dc25c17a"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-01dc25c17a", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2216,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2335,7 +2225,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-01dc25c17a", "asset_type": "factory"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-01dc25c17a", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2345,23 +2235,23 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E22" t="n">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-01dc25c17a", "asset_type": "production_line"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2371,14 +2261,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E23" t="n">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2387,7 +2277,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2404,11 +2294,11 @@
         <v>-14</v>
       </c>
       <c r="E24" t="n">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2423,23 +2313,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-36</v>
+        <v>-14</v>
       </c>
       <c r="E25" t="n">
-        <v>337</v>
+        <v>371</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2449,23 +2339,23 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>313</v>
+        <v>357</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-f3d8559ce5", "line_id": "L-01dc25c17a", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2475,23 +2365,23 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E27" t="n">
-        <v>299</v>
+        <v>342</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-01dc25c17a"}</t>
         </is>
       </c>
     </row>
@@ -2501,23 +2391,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>285</v>
+        <v>342</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-01dc25c17a", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2527,14 +2417,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>285</v>
+        <v>342</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2543,7 +2433,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 60.0, "order_id": "SIM_XA_FIXED-3-0168", "receivable_term_quarters": 3, "revenue_wan": 76.0}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-01dc25c17a", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2553,23 +2443,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-36</v>
+        <v>-4</v>
       </c>
       <c r="E30" t="n">
-        <v>249</v>
+        <v>338</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 36.0, "material_id": "R1", "quantity": 3.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2579,23 +2469,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>-24</v>
+        <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>225</v>
+        <v>324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 60.0, "job_id": "JOB-21c5c8c587", "line_id": "L-01dc25c17a", "product_id": "P1", "quantity": 3.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2612,11 +2502,11 @@
         <v>-14</v>
       </c>
       <c r="E32" t="n">
-        <v>211</v>
+        <v>310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2631,23 +2521,23 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E33" t="n">
-        <v>196</v>
+        <v>296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-01dc25c17a"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2657,23 +2547,23 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E34" t="n">
-        <v>196</v>
+        <v>282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-01dc25c17a", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2683,23 +2573,23 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E35" t="n">
-        <v>196</v>
+        <v>267</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-01dc25c17a", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-01dc25c17a"}</t>
         </is>
       </c>
     </row>
@@ -2709,23 +2599,23 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>184</v>
+        <v>267</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-01dc25c17a", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2735,23 +2625,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
-        <v>170</v>
+        <v>267</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-01dc25c17a", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2761,23 +2651,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="E38" t="n">
-        <v>156</v>
+        <v>263</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2787,23 +2677,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>76</v>
+        <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-7ebb52411d"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2820,11 +2710,11 @@
         <v>-14</v>
       </c>
       <c r="E40" t="n">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2839,23 +2729,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E41" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-4-0138", "receivable_term_quarters": 4, "revenue_wan": 61.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2865,23 +2755,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="E42" t="n">
         <v>206</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
+          <t>maintenance_expense | {"line_id": "L-01dc25c17a"}</t>
         </is>
       </c>
     </row>
@@ -2891,23 +2781,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-24fe0c9ad2", "line_id": "L-01dc25c17a", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-01dc25c17a", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2917,307 +2807,21 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="n">
-        <v>42</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Pay_Maintenance</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E45" t="n">
-        <v>169</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>第4年4季</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>maintenance_expense | {"line_id": "L-01dc25c17a"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="n">
-        <v>43</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="n">
-        <v>169</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>第4年4季</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-01dc25c17a", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="n">
-        <v>44</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="n">
-        <v>169</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>第4年4季</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-01dc25c17a", "asset_type": "production_line"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" t="n">
-        <v>45</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Pay_AD</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>-12</v>
-      </c>
-      <c r="E48" t="n">
-        <v>157</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" t="n">
-        <v>46</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E49" t="n">
-        <v>143</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="n">
-        <v>47</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E50" t="n">
-        <v>129</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>第5年2季</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="n">
-        <v>48</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E51" t="n">
-        <v>115</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="n">
-        <v>49</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Update_Receivable</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>61</v>
-      </c>
-      <c r="E52" t="n">
-        <v>176</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>receivable_collected | {"receivable_id": "AR-902d1f2990"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="n">
-        <v>50</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Pay_Maintenance</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E53" t="n">
-        <v>161</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>maintenance_expense | {"line_id": "L-01dc25c17a"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="n">
-        <v>51</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>161</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-01dc25c17a", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="n">
-        <v>52</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>161</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-01dc25c17a", "asset_type": "production_line"}</t>
         </is>
@@ -3324,16 +2928,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3549,16 +3153,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H13" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -3614,10 +3218,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -3639,10 +3243,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3664,10 +3268,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -3686,16 +3290,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H19" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -3711,16 +3315,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-83</v>
+        <v>-75</v>
       </c>
       <c r="F20" t="n">
-        <v>-67</v>
+        <v>-75</v>
       </c>
       <c r="G20" t="n">
-        <v>-62</v>
+        <v>-75</v>
       </c>
       <c r="H20" t="n">
-        <v>-69</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="21">
@@ -3761,16 +3365,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-98.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-82.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-77.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-84.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="23">
@@ -3811,16 +3415,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-108.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-82.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-77.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-84.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="25">
@@ -3861,16 +3465,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-108.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-82.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-77.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-84.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="28">
@@ -3960,16 +3564,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="F30" t="n">
-        <v>196</v>
+        <v>342</v>
       </c>
       <c r="G30" t="n">
-        <v>169</v>
+        <v>267</v>
       </c>
       <c r="H30" t="n">
-        <v>161</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31">
@@ -3988,10 +3592,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>76</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -4013,10 +3617,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -4041,10 +3645,10 @@
         <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -4085,16 +3689,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>399</v>
+        <v>417</v>
       </c>
       <c r="F35" t="n">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="G35" t="n">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H35" t="n">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36">
@@ -4210,16 +3814,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>480.6</v>
+        <v>498.6</v>
       </c>
       <c r="F40" t="n">
-        <v>398.4</v>
+        <v>408.4</v>
       </c>
       <c r="G40" t="n">
-        <v>321.2</v>
+        <v>318.2</v>
       </c>
       <c r="H40" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41">
@@ -4388,13 +3992,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-194.4</v>
+        <v>-176.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-276.6</v>
+        <v>-266.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-353.8</v>
+        <v>-356.8</v>
       </c>
     </row>
     <row r="48">
@@ -4410,16 +4014,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-108.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-82.2</v>
+        <v>-90.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-77.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-84.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="49">
@@ -4435,16 +4039,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>480.6</v>
+        <v>498.6</v>
       </c>
       <c r="F49" t="n">
-        <v>398.4</v>
+        <v>408.4</v>
       </c>
       <c r="G49" t="n">
-        <v>321.2</v>
+        <v>318.2</v>
       </c>
       <c r="H49" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50">
@@ -4460,16 +4064,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>480.6</v>
+        <v>498.6</v>
       </c>
       <c r="F50" t="n">
-        <v>398.4</v>
+        <v>408.4</v>
       </c>
       <c r="G50" t="n">
-        <v>321.2</v>
+        <v>318.2</v>
       </c>
       <c r="H50" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4540,7 +4144,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4689,7 +4293,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4838,7 +4442,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4987,7 +4591,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5136,7 +4740,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
